--- a/학교 중간.xlsx
+++ b/학교 중간.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A597511B-9F53-45E2-BBA2-A6AEF74DD809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4B019E-5B6E-436E-975E-A7A9F6DEA320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
   <si>
     <t>교시</t>
   </si>
@@ -73,6 +73,14 @@
   </si>
   <si>
     <t>5(13:00)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공통영어</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>화학2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -201,22 +209,22 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -557,37 +565,37 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2">
-        <v>2</v>
+        <v>302</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="F2" s="2">
-        <v>2</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6"/>
+      <c r="A3" s="7"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="10" t="s">
+      <c r="F3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="10" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2"/>
@@ -597,7 +605,7 @@
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6"/>
+      <c r="A5" s="7"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -605,96 +613,96 @@
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="D6" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E6" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F6" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="6"/>
+      <c r="A7" s="7"/>
       <c r="B7" s="3"/>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="E7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="F7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
       <c r="D8" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="6"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="10" t="s">
+      <c r="A9" s="7"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="9"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="6"/>
+      <c r="A11" s="7"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="9"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="6"/>
+      <c r="A13" s="7"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
@@ -718,6 +726,9 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="E12:E13"/>
@@ -727,9 +738,6 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
